--- a/output/graficos_dimensiones/comunal_m_movinterna_a_2024_antofagasta.xlsx
+++ b/output/graficos_dimensiones/comunal_m_movinterna_a_2024_antofagasta.xlsx
@@ -69,7 +69,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-06 19:39</t>
+    <t xml:space="preserve">2026-09-09 22:25</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_m_movinterna_a_2024_antofagasta.xlsx
+++ b/output/graficos_dimensiones/comunal_m_movinterna_a_2024_antofagasta.xlsx
@@ -69,7 +69,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-09 22:25</t>
+    <t xml:space="preserve">2026-09-12 19:42</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_m_movinterna_a_2024_antofagasta.xlsx
+++ b/output/graficos_dimensiones/comunal_m_movinterna_a_2024_antofagasta.xlsx
@@ -69,7 +69,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-12 19:42</t>
+    <t xml:space="preserve">2026-09-24 00:19</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_m_movinterna_a_2024_antofagasta.xlsx
+++ b/output/graficos_dimensiones/comunal_m_movinterna_a_2024_antofagasta.xlsx
@@ -69,7 +69,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-24 00:19</t>
+    <t xml:space="preserve">2026-09-27 22:08</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_m_movinterna_a_2024_antofagasta.xlsx
+++ b/output/graficos_dimensiones/comunal_m_movinterna_a_2024_antofagasta.xlsx
@@ -69,7 +69,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-27 22:08</t>
+    <t xml:space="preserve">2026-09-29 11:03</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -505,7 +505,7 @@
         <v>2024</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>53.93</v>
+        <v>539.27</v>
       </c>
     </row>
     <row r="3">
@@ -522,7 +522,7 @@
         <v>2024</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>33.09</v>
+        <v>330.87</v>
       </c>
     </row>
     <row r="4">
@@ -539,7 +539,7 @@
         <v>2024</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>27.23</v>
+        <v>272.3</v>
       </c>
     </row>
     <row r="5">
@@ -556,7 +556,7 @@
         <v>2024</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>25.21</v>
+        <v>252.13</v>
       </c>
     </row>
     <row r="6">
@@ -573,7 +573,7 @@
         <v>2024</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>19.86</v>
+        <v>198.56</v>
       </c>
     </row>
     <row r="7">
@@ -590,7 +590,7 @@
         <v>2024</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>16.46</v>
+        <v>164.59</v>
       </c>
     </row>
     <row r="8">
@@ -607,7 +607,7 @@
         <v>2024</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>13.62</v>
+        <v>136.21</v>
       </c>
     </row>
     <row r="9">
@@ -624,7 +624,7 @@
         <v>2024</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>11.62</v>
+        <v>116.21</v>
       </c>
     </row>
     <row r="10">
@@ -641,7 +641,7 @@
         <v>2024</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>9.12</v>
+        <v>91.22</v>
       </c>
     </row>
   </sheetData>

--- a/output/graficos_dimensiones/comunal_m_movinterna_a_2024_antofagasta.xlsx
+++ b/output/graficos_dimensiones/comunal_m_movinterna_a_2024_antofagasta.xlsx
@@ -69,7 +69,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-29 11:03</t>
+    <t xml:space="preserve">2026-10-01 19:28</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -87,7 +87,7 @@
     <t xml:space="preserve">Indicador</t>
   </si>
   <si>
-    <t xml:space="preserve">Movilidad interna (CMI)</t>
+    <t xml:space="preserve">Movilidad interna comunal (CMI)</t>
   </si>
   <si>
     <t xml:space="preserve">Unidad territorial</t>

--- a/output/graficos_dimensiones/comunal_m_movinterna_a_2024_antofagasta.xlsx
+++ b/output/graficos_dimensiones/comunal_m_movinterna_a_2024_antofagasta.xlsx
@@ -69,7 +69,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-01 19:28</t>
+    <t xml:space="preserve">2026-10-02 13:01</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_m_movinterna_a_2024_antofagasta.xlsx
+++ b/output/graficos_dimensiones/comunal_m_movinterna_a_2024_antofagasta.xlsx
@@ -69,7 +69,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-02 13:01</t>
+    <t xml:space="preserve">2026-10-05 07:37</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
